--- a/RSVMultipleEpisodesWorkbook.xlsx
+++ b/RSVMultipleEpisodesWorkbook.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iangalbreath/Documents/GitHub/RSV-asthma-US/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D07C5EE-7563-2247-83A4-4B1D50B5323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2564DC3C-121A-0043-AB12-547F519E9DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="28480" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicaid" sheetId="1" r:id="rId1"/>
     <sheet name="MarketScan Commercial CCAE" sheetId="2" r:id="rId2"/>
     <sheet name="Optum Clinformatics" sheetId="3" r:id="rId3"/>
+    <sheet name="worksheet" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="40">
   <si>
     <t>MEDICAID</t>
   </si>
@@ -245,11 +246,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -593,38 +594,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="8"/>
       <c r="C8" t="s">
         <v>2</v>
       </c>
@@ -654,16 +655,16 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="I9" s="7" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="I9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
       <c r="L9" t="s">
         <v>7</v>
       </c>
@@ -1159,10 +1160,10 @@
       <c r="Q21" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="8"/>
       <c r="L23" t="s">
         <v>7</v>
       </c>
@@ -1763,12 +1764,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2:P2" r:id="rId1" display="INFORMATION FROM THIS WORKBOOK SOURCE FROM GANTENBERG ET. ALL REGARDING HEALTHCARE UTILIZATION DURING ACUTE MA EPISODES OF RSV-LRTI AMONG INFANTS IN UNITED STATES - TABLE 2" xr:uid="{68972C1E-92F2-3243-8245-6BF265D22500}"/>
@@ -1783,19 +1784,19 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="8"/>
       <c r="C2" t="s">
         <v>2</v>
       </c>
@@ -1825,16 +1826,16 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="I3" s="7" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
       <c r="L3" t="s">
         <v>7</v>
       </c>
@@ -2263,10 +2264,10 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="L15" t="s">
         <v>7</v>
       </c>
@@ -2706,19 +2707,19 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="6" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="8"/>
       <c r="E7" t="s">
         <v>2</v>
       </c>
@@ -2748,16 +2749,16 @@
       </c>
     </row>
     <row r="8" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="K8" s="7" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" t="s">
         <v>7</v>
       </c>
@@ -3186,10 +3187,10 @@
       </c>
     </row>
     <row r="20" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="7"/>
+      <c r="D20" s="8"/>
       <c r="N20" t="s">
         <v>7</v>
       </c>
@@ -3614,4 +3615,1366 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F776ED3D-B944-E94D-B8A2-49FD322B3DA2}">
+  <dimension ref="C4:AA29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="4" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="E4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+    </row>
+    <row r="6" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="G6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="L6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8"/>
+      <c r="S6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>52348</v>
+      </c>
+      <c r="F7">
+        <v>48199</v>
+      </c>
+      <c r="G7">
+        <v>0.3</v>
+      </c>
+      <c r="H7">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="I7">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="K7">
+        <f>G7*E7</f>
+        <v>15704.4</v>
+      </c>
+      <c r="L7">
+        <f>H7*E7</f>
+        <v>27378.004000000001</v>
+      </c>
+      <c r="M7">
+        <f>I7*E7</f>
+        <v>9265.5959999999995</v>
+      </c>
+      <c r="N7">
+        <f>L7+M7</f>
+        <v>36643.599999999999</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="Y7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+    </row>
+    <row r="8" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>27011</v>
+      </c>
+      <c r="G8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H8">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="I8">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="K8">
+        <f>G8*E7</f>
+        <v>28791.4</v>
+      </c>
+      <c r="L8">
+        <f>H8*E7</f>
+        <v>20520.416000000001</v>
+      </c>
+      <c r="M8">
+        <f>I8*E7</f>
+        <v>3088.5319999999997</v>
+      </c>
+      <c r="N8">
+        <f>L8+M8</f>
+        <v>23608.948</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>12</v>
+      </c>
+      <c r="R8" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8">
+        <v>19496</v>
+      </c>
+      <c r="T8">
+        <v>21865</v>
+      </c>
+      <c r="U8">
+        <v>0.182</v>
+      </c>
+      <c r="V8">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="W8">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="Y8">
+        <f>19496*U8</f>
+        <v>3548.2719999999999</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" ref="Z8:AA8" si="0">19496*V8</f>
+        <v>11190.704</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>4757.0240000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>9684</v>
+      </c>
+      <c r="G9">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="H9">
+        <v>0.161</v>
+      </c>
+      <c r="I9">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K9">
+        <f>G9*E7</f>
+        <v>43291.795999999995</v>
+      </c>
+      <c r="L9">
+        <f>H9*E7</f>
+        <v>8428.0280000000002</v>
+      </c>
+      <c r="M9">
+        <f>I9*E7</f>
+        <v>628.17600000000004</v>
+      </c>
+      <c r="N9">
+        <f>M9+L9</f>
+        <v>9056.2039999999997</v>
+      </c>
+      <c r="R9" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9">
+        <v>6829</v>
+      </c>
+      <c r="U9">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="V9">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="W9">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" ref="Y9:Y10" si="1">19496*U9</f>
+        <v>13315.768000000002</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" ref="Z9:Z10" si="2">19496*V9</f>
+        <v>5556.36</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" ref="AA9:AA10" si="3">19496*W9</f>
+        <v>604.37599999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>2649</v>
+      </c>
+      <c r="F10">
+        <v>2015</v>
+      </c>
+      <c r="G10">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="H10">
+        <v>0.442</v>
+      </c>
+      <c r="I10">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="K10">
+        <f>2649*G10</f>
+        <v>1094.037</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ref="L10:M10" si="4">2649*H10</f>
+        <v>1170.8579999999999</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>384.10499999999996</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ref="N10:N15" si="5">M10+L10</f>
+        <v>1554.963</v>
+      </c>
+      <c r="R10" t="s">
+        <v>15</v>
+      </c>
+      <c r="T10">
+        <v>4109</v>
+      </c>
+      <c r="U10">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="V10">
+        <v>0.18</v>
+      </c>
+      <c r="W10">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="1"/>
+        <v>15694.28</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="2"/>
+        <v>3509.2799999999997</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="3"/>
+        <v>292.44</v>
+      </c>
+    </row>
+    <row r="11" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>1311</v>
+      </c>
+      <c r="G11">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="H11">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="I11">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ref="K11:K12" si="6">2649*G11</f>
+        <v>1488.7380000000001</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ref="L11:L12" si="7">2649*H11</f>
+        <v>1025.163</v>
+      </c>
+      <c r="M11">
+        <f t="shared" ref="M11:M12" si="8">2649*I11</f>
+        <v>137.74799999999999</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>1162.9110000000001</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11">
+        <v>978</v>
+      </c>
+      <c r="T11">
+        <v>992</v>
+      </c>
+      <c r="U11">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="Y11">
+        <f>U11*978</f>
+        <v>253.30200000000002</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" ref="Z11:AA11" si="9">V11*978</f>
+        <v>503.67</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="9"/>
+        <v>221.02800000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>1057</v>
+      </c>
+      <c r="G12">
+        <v>0.63</v>
+      </c>
+      <c r="H12">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I12">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="6"/>
+        <v>1668.8700000000001</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="7"/>
+        <v>903.30900000000008</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="8"/>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>977.48100000000011</v>
+      </c>
+      <c r="R12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T12">
+        <v>379</v>
+      </c>
+      <c r="U12">
+        <v>0.65</v>
+      </c>
+      <c r="V12">
+        <v>0.316</v>
+      </c>
+      <c r="W12">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" ref="Y12:Y13" si="10">U12*978</f>
+        <v>635.70000000000005</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" ref="Z12:Z13" si="11">V12*978</f>
+        <v>309.048</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" ref="AA12:AA13" si="12">W12*978</f>
+        <v>33.252000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>12360</v>
+      </c>
+      <c r="F13">
+        <v>10201</v>
+      </c>
+      <c r="G13">
+        <v>0.371</v>
+      </c>
+      <c r="H13">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="I13">
+        <v>0.155</v>
+      </c>
+      <c r="K13">
+        <f>12360*G13</f>
+        <v>4585.5600000000004</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:M13" si="13">12360*H13</f>
+        <v>5871</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="13"/>
+        <v>1915.8</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>7786.8</v>
+      </c>
+      <c r="R13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13">
+        <v>345</v>
+      </c>
+      <c r="U13">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="V13">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="W13">
+        <v>2.4E-2</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="10"/>
+        <v>656.23800000000006</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="11"/>
+        <v>299.26799999999997</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="12"/>
+        <v>23.472000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>6784</v>
+      </c>
+      <c r="G14">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="H14">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="I14">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ref="K14:K15" si="14">12360*G14</f>
+        <v>6464.2800000000007</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:L15" si="15">12360*H14</f>
+        <v>5104.6799999999994</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14:M15" si="16">12360*I14</f>
+        <v>803.4</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>5908.079999999999</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14">
+        <v>4935</v>
+      </c>
+      <c r="T14">
+        <v>5295</v>
+      </c>
+      <c r="U14">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="V14">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="W14">
+        <v>0.245</v>
+      </c>
+      <c r="Y14">
+        <f>4935*U14</f>
+        <v>1169.595</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" ref="Z14:AA14" si="17">4935*V14</f>
+        <v>2556.33</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="17"/>
+        <v>1209.075</v>
+      </c>
+    </row>
+    <row r="15" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15">
+        <v>3905</v>
+      </c>
+      <c r="G15">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="H15">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="I15">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="14"/>
+        <v>8738.52</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="15"/>
+        <v>3349.5600000000004</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="16"/>
+        <v>271.91999999999996</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>3621.4800000000005</v>
+      </c>
+      <c r="R15" t="s">
+        <v>14</v>
+      </c>
+      <c r="T15">
+        <v>1962</v>
+      </c>
+      <c r="U15">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="V15">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="W15">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" ref="Y15:Y16" si="18">4935*U15</f>
+        <v>3168.27</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" ref="Z15:Z16" si="19">4935*V15</f>
+        <v>1584.135</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" ref="AA15:AA16" si="20">4935*W15</f>
+        <v>182.595</v>
+      </c>
+    </row>
+    <row r="16" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="R16" t="s">
+        <v>15</v>
+      </c>
+      <c r="T16">
+        <v>1525</v>
+      </c>
+      <c r="U16">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="V16">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="W16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="18"/>
+        <v>3543.33</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="19"/>
+        <v>1263.3600000000001</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="20"/>
+        <v>128.31</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>2</v>
+      </c>
+      <c r="T19" t="s">
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>2</v>
+      </c>
+      <c r="X19" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="G20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="L20" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" s="8"/>
+      <c r="U20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="Y20" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21">
+        <v>132070</v>
+      </c>
+      <c r="F21">
+        <v>120933</v>
+      </c>
+      <c r="G21">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="H21">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="I21">
+        <v>0.17</v>
+      </c>
+      <c r="K21">
+        <f>G21*132070</f>
+        <v>38168.229999999996</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ref="L21:M21" si="21">H21*132070</f>
+        <v>71449.87000000001</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="21"/>
+        <v>22451.9</v>
+      </c>
+      <c r="N21">
+        <f>L21+M21</f>
+        <v>93901.770000000019</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>12</v>
+      </c>
+      <c r="R21" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>53099</v>
+      </c>
+      <c r="T21">
+        <v>63580</v>
+      </c>
+      <c r="U21">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="V21">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="W21">
+        <v>0.24</v>
+      </c>
+      <c r="Y21">
+        <f>U21*53099</f>
+        <v>5203.7020000000002</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" ref="Z21:AA21" si="22">V21*53099</f>
+        <v>35151.538</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="22"/>
+        <v>12743.76</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>61831</v>
+      </c>
+      <c r="G22">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H22">
+        <v>0.376</v>
+      </c>
+      <c r="I22">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" ref="K22:K23" si="23">G22*132070</f>
+        <v>76600.599999999991</v>
+      </c>
+      <c r="L22">
+        <f t="shared" ref="L22:L23" si="24">H22*132070</f>
+        <v>49658.32</v>
+      </c>
+      <c r="M22">
+        <f t="shared" ref="M22:M23" si="25">I22*132070</f>
+        <v>5811.08</v>
+      </c>
+      <c r="N22">
+        <f t="shared" ref="N22:N29" si="26">L22+M22</f>
+        <v>55469.4</v>
+      </c>
+      <c r="R22" t="s">
+        <v>14</v>
+      </c>
+      <c r="T22">
+        <v>12400</v>
+      </c>
+      <c r="U22">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="V22">
+        <v>0.192</v>
+      </c>
+      <c r="W22">
+        <v>0.02</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" ref="Y22:Y23" si="27">U22*53099</f>
+        <v>41842.012000000002</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" ref="Z22:Z23" si="28">V22*53099</f>
+        <v>10195.008</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" ref="AA22:AA23" si="29">W22*53099</f>
+        <v>1061.98</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>13797</v>
+      </c>
+      <c r="G23">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="H23">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="I23">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="23"/>
+        <v>119127.14</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="24"/>
+        <v>12018.369999999999</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="25"/>
+        <v>924.49</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="26"/>
+        <v>12942.859999999999</v>
+      </c>
+      <c r="R23" t="s">
+        <v>15</v>
+      </c>
+      <c r="T23">
+        <v>5354</v>
+      </c>
+      <c r="U23">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="V23">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="W23">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="27"/>
+        <v>48107.694000000003</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="28"/>
+        <v>4619.6129999999994</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="29"/>
+        <v>371.69299999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>7692</v>
+      </c>
+      <c r="F24">
+        <v>5613</v>
+      </c>
+      <c r="G24">
+        <v>0.435</v>
+      </c>
+      <c r="H24">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="K24">
+        <f>G24*7692</f>
+        <v>3346.02</v>
+      </c>
+      <c r="L24">
+        <f t="shared" ref="L24:M24" si="30">H24*7692</f>
+        <v>3299.8679999999999</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="30"/>
+        <v>1046.1120000000001</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="26"/>
+        <v>4345.9799999999996</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>16</v>
+      </c>
+      <c r="R24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24">
+        <v>2853</v>
+      </c>
+      <c r="T24">
+        <v>2998</v>
+      </c>
+      <c r="U24">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.53</v>
+      </c>
+      <c r="W24">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="Y24">
+        <f>U24*2853</f>
+        <v>681.86699999999996</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" ref="Z24:AA24" si="31">V24*2853</f>
+        <v>1512.0900000000001</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="31"/>
+        <v>659.04300000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25">
+        <v>3758</v>
+      </c>
+      <c r="G25">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="H25">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="I25">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ref="K25:K26" si="32">G25*7692</f>
+        <v>4276.7520000000004</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ref="L25:L26" si="33">H25*7692</f>
+        <v>3099.8760000000002</v>
+      </c>
+      <c r="M25">
+        <f t="shared" ref="M25:M26" si="34">I25*7692</f>
+        <v>315.37200000000001</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="26"/>
+        <v>3415.248</v>
+      </c>
+      <c r="R25" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25">
+        <v>865</v>
+      </c>
+      <c r="U25">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="V25">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="W25">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" ref="Y25:Y26" si="35">U25*2853</f>
+        <v>2057.0129999999999</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" ref="Z25:Z26" si="36">V25*2853</f>
+        <v>733.221</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" ref="AA25:AA26" si="37">W25*2853</f>
+        <v>62.765999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>2501</v>
+      </c>
+      <c r="G26">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="H26">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="I26">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="32"/>
+        <v>5322.8639999999996</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="33"/>
+        <v>2238.3719999999998</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="34"/>
+        <v>130.76400000000001</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="26"/>
+        <v>2369.136</v>
+      </c>
+      <c r="R26" t="s">
+        <v>15</v>
+      </c>
+      <c r="T26">
+        <v>800</v>
+      </c>
+      <c r="U26">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.249</v>
+      </c>
+      <c r="W26">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="35"/>
+        <v>2096.9549999999999</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="36"/>
+        <v>710.39700000000005</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="37"/>
+        <v>45.648000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>30982</v>
+      </c>
+      <c r="F27">
+        <v>26269</v>
+      </c>
+      <c r="G27">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="H27">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0.16</v>
+      </c>
+      <c r="K27">
+        <f>G27*30982</f>
+        <v>10781.735999999999</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ref="L27:M29" si="38">H27*30982</f>
+        <v>15243.144</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="38"/>
+        <v>4957.12</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="26"/>
+        <v>20200.263999999999</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>17</v>
+      </c>
+      <c r="R27" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27">
+        <v>13116</v>
+      </c>
+      <c r="T27">
+        <v>15549</v>
+      </c>
+      <c r="U27">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="W27">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="Y27">
+        <f>U27*13116</f>
+        <v>1823.1240000000003</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" ref="Z27:AA27" si="39">V27*13116</f>
+        <v>7895.8319999999994</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="39"/>
+        <v>3397.0440000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>15754</v>
+      </c>
+      <c r="G28">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="H28">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="I28">
+        <v>0.05</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ref="K28:K29" si="40">G28*30982</f>
+        <v>16916.172000000002</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="38"/>
+        <v>12516.728000000001</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="38"/>
+        <v>1549.1000000000001</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="26"/>
+        <v>14065.828000000001</v>
+      </c>
+      <c r="R28" t="s">
+        <v>14</v>
+      </c>
+      <c r="T28">
+        <v>3593</v>
+      </c>
+      <c r="U28">
+        <v>0.753</v>
+      </c>
+      <c r="V28">
+        <v>0.222</v>
+      </c>
+      <c r="W28">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" ref="Y28:Y29" si="41">U28*13116</f>
+        <v>9876.348</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" ref="Z28:Z29" si="42">V28*13116</f>
+        <v>2911.752</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" ref="AA28:AA29" si="43">W28*13116</f>
+        <v>327.90000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>6039</v>
+      </c>
+      <c r="G29">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="H29">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="I29">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="40"/>
+        <v>25343.275999999998</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="38"/>
+        <v>5235.9580000000005</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="38"/>
+        <v>402.76599999999996</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="26"/>
+        <v>5638.7240000000002</v>
+      </c>
+      <c r="R29" t="s">
+        <v>15</v>
+      </c>
+      <c r="T29">
+        <v>2199</v>
+      </c>
+      <c r="U29">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="V29">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="W29">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="41"/>
+        <v>11069.904</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="42"/>
+        <v>1888.704</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="43"/>
+        <v>157.392</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G20:I20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RSVMultipleEpisodesWorkbook.xlsx
+++ b/RSVMultipleEpisodesWorkbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iangalbreath/Documents/GitHub/RSV-asthma-US/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2564DC3C-121A-0043-AB12-547F519E9DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA92F3-5641-A84F-A78E-00E30D3BCBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicaid" sheetId="1" r:id="rId1"/>
@@ -213,12 +213,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -234,7 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -246,12 +252,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -594,38 +602,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="7"/>
       <c r="C8" t="s">
         <v>2</v>
       </c>
@@ -655,16 +663,16 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="I9" s="8" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="I9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
       <c r="L9" t="s">
         <v>7</v>
       </c>
@@ -1160,10 +1168,10 @@
       <c r="Q21" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="8"/>
+      <c r="B23" s="7"/>
       <c r="L23" t="s">
         <v>7</v>
       </c>
@@ -1639,19 +1647,19 @@
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="M35">
+      <c r="M35" s="9">
         <f>C34+'MarketScan Commercial CCAE'!C25</f>
         <v>239812</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="9">
         <f>H34+'MarketScan Commercial CCAE'!H25</f>
         <v>363833</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="9">
         <f>N35-M35</f>
         <v>124021</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="10">
         <f>O35/N35</f>
         <v>0.34087342269667675</v>
       </c>
@@ -1784,19 +1792,19 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" t="s">
         <v>2</v>
       </c>
@@ -1826,16 +1834,16 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="I3" s="8" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
       <c r="L3" t="s">
         <v>7</v>
       </c>
@@ -2264,10 +2272,10 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="7"/>
       <c r="L15" t="s">
         <v>7</v>
       </c>
@@ -2707,19 +2715,19 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="6" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="7"/>
       <c r="E7" t="s">
         <v>2</v>
       </c>
@@ -2749,16 +2757,16 @@
       </c>
     </row>
     <row r="8" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="K8" s="8" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="K8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
       <c r="N8" t="s">
         <v>7</v>
       </c>
@@ -3187,10 +3195,10 @@
       </c>
     </row>
     <row r="20" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="7"/>
       <c r="N20" t="s">
         <v>7</v>
       </c>
@@ -3623,19 +3631,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="7"/>
       <c r="E5" t="s">
         <v>2</v>
       </c>
@@ -3663,27 +3671,27 @@
       <c r="M5">
         <v>2</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
     </row>
     <row r="6" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
       <c r="L6" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="R6" s="8"/>
+      <c r="R6" s="7"/>
       <c r="S6" t="s">
         <v>2</v>
       </c>
@@ -3750,16 +3758,16 @@
         <f>L7+M7</f>
         <v>36643.599999999999</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="U7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="Y7" s="8" t="s">
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="Y7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="3:27" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
@@ -4301,10 +4309,10 @@
       </c>
     </row>
     <row r="19" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="8"/>
+      <c r="D19" s="7"/>
       <c r="E19" t="s">
         <v>2</v>
       </c>
@@ -4361,28 +4369,28 @@
       </c>
     </row>
     <row r="20" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
       <c r="L20" t="s">
         <v>6</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="R20" s="8"/>
-      <c r="U20" s="8" t="s">
+      <c r="R20" s="7"/>
+      <c r="U20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="Y20" s="8" t="s">
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="Y20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
     </row>
     <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
